--- a/foxconn/dist/20261028_鴻海個股模型_v0.3.xlsx
+++ b/foxconn/dist/20261028_鴻海個股模型_v0.3.xlsx
@@ -7446,26 +7446,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7664,26 +7664,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7785,26 +7785,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7906,26 +7906,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8027,26 +8027,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8148,26 +8148,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/foxconn/dist/20261028_鴻海個股模型_v0.3.xlsx
+++ b/foxconn/dist/20261028_鴻海個股模型_v0.3.xlsx
@@ -6660,26 +6660,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8234,26 +8234,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8351,26 +8351,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8493,26 +8493,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8614,26 +8614,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8784,26 +8784,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -20284,26 +20284,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
